--- a/DCZ/touch_rect_log_20260610_161622.xlsx
+++ b/DCZ/touch_rect_log_20260610_161622.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\logs\294\DCZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EtoHayato\Desktop\git_repository\294\DCZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{90024217-9C4E-4ED3-8FC8-BF843EC739E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D040B2C-97B5-44BE-85A5-5310101C5A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="825" windowWidth="25785" windowHeight="15375" activeTab="1" xr2:uid="{72DE281A-2B90-4D14-BA96-0EE41E4125CB}"/>
+    <workbookView xWindow="18540" yWindow="2250" windowWidth="25455" windowHeight="14670" activeTab="1" xr2:uid="{72DE281A-2B90-4D14-BA96-0EE41E4125CB}"/>
   </bookViews>
   <sheets>
     <sheet name="touch_rect_log_20260610_161622" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">touch_rect_log_20260610_161622!$A$1:$P$1979</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6136,7 +6149,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -6728,7 +6741,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6828,7 +6841,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t> DCZ 0.1 ug/kg</a:t>
+              <a:t> DCZ 1 ug/kg</a:t>
             </a:r>
             <a:endParaRPr lang="ja-JP" altLang="en-US"/>
           </a:p>
@@ -6859,7 +6872,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -9090,16 +9103,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>604837</xdr:colOff>
-      <xdr:row>184</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>185737</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>61911</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>376237</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>200024</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
